--- a/선수_SPID_목록.xlsx
+++ b/선수_SPID_목록.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,312 +431,432 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>866255205</t>
+          <t>868247703</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S. 버랄터</t>
+          <t>이언 러시</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>866231913</t>
+          <t>867229391</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. 아우르스네스</t>
+          <t>팔리냐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>866264388</t>
+          <t>868107715</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>몰레이로</t>
+          <t>루시우</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>866198705</t>
+          <t>867186537</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>안디 나하르</t>
+          <t>C. 스투아니</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>866277809</t>
+          <t>867210413</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>K. 고다이</t>
+          <t>알레시오 로마뇰리</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>866226807</t>
+          <t>868052241</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>크리스천 롤던</t>
+          <t>헨릭 라르손</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>866247257</t>
+          <t>867208135</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이바녜스</t>
+          <t>압둘라예 두쿠레</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>866247228</t>
+          <t>868191208</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>데인 생클레어</t>
+          <t>차범근</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>866279015</t>
+          <t>868233700</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V. 프로홀트</t>
+          <t>잔루카 비알리</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>866243169</t>
+          <t>867240716</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Y. 베그라위</t>
+          <t>M. 올리베라</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>866261478</t>
+          <t>867139869</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T. 두비카스</t>
+          <t>베슬리 스네이더</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>866079027</t>
+          <t>867214101</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>로날트 쿠만 Jr.</t>
+          <t>파울루 푸트리</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>866193698</t>
+          <t>867157481</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>올리버 바우만</t>
+          <t>라울 알비올</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>866243830</t>
+          <t>867242453</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>말리송</t>
+          <t>S. 반덴베르흐</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>866267991</t>
+          <t>867236480</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M. 페로네</t>
+          <t>이브 비수마</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>866254817</t>
+          <t>867231591</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M. 아라우호</t>
+          <t>하비 갈란</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>866262311</t>
+          <t>868222481</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B. 반로에이</t>
+          <t>로랑 블랑</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>866275138</t>
+          <t>868135455</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>라민 카마라</t>
+          <t>마이콘</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>866264862</t>
+          <t>867239580</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M. 아킬로셰</t>
+          <t>브레메르</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>866246826</t>
+          <t>867256079</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T. 와타나베</t>
+          <t>M. 카이세도</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>866233400</t>
+          <t>867210455</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>J. 글레스네스</t>
+          <t>조니</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>866240834</t>
+          <t>867192816</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L. 차레비치</t>
+          <t>레안드로 카브레라</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>866265693</t>
+          <t>867199503</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J. 키비오르</t>
+          <t>그라니트 자카</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>866262580</t>
+          <t>867051412</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D. 네야슈미치</t>
+          <t>팀 케이힐</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>866242596</t>
+          <t>867208461</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T. 블랙먼</t>
+          <t>마르턴 더론</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>866259399</t>
+          <t>868045674</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>라스무스 호일룬</t>
+          <t>마이클 에시앙</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>867208333</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>엠레 잔</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>867173030</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>오스카르 트레호</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>867250723</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>K. 코네</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>867241096</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>산드로 토날리</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>867193254</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>크리스토퍼 트리멜</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>867135455</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>마이콘</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>868140601</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>네마냐 비디치</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>867236015</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M. 깁스-화이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>867203263</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>해리 매과이어</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>867000027</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>조 콜</t>
         </is>
       </c>
     </row>
